--- a/templates/INFRA ADV II - template.xlsx
+++ b/templates/INFRA ADV II - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
@@ -1408,96 +1408,96 @@
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>1.045364700866</v>
+        <v>1.047301643462</v>
       </c>
       <c r="D17" s="37" t="n">
-        <v>0.0002223012284494619</v>
+        <v>0.0004269899983553316</v>
       </c>
       <c r="E17" s="37" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>0.4096492495015987</v>
+        <v>0.7868428509863858</v>
       </c>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B18" s="39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>1.045132366657</v>
+        <v>1.046854646998</v>
       </c>
       <c r="D18" s="41" t="n">
-        <v>0.0005362004429361189</v>
+        <v>0.0005614747018005684</v>
       </c>
       <c r="E18" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>0.988092196175795</v>
+        <v>1.034666752905627</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B19" s="39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>1.044572266545</v>
+        <v>1.046267194437</v>
       </c>
       <c r="D19" s="41" t="n">
-        <v>0.0004664094036868072</v>
+        <v>0.0006547669893584018</v>
       </c>
       <c r="E19" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>0.8594836093054944</v>
+        <v>1.206582652106527</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>1.044085295345</v>
+        <v>1.045582581478</v>
       </c>
       <c r="D20" s="41" t="n">
-        <v>0.0006207229277350734</v>
+        <v>-0.001055780801041517</v>
       </c>
       <c r="E20" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>1.143847396924826</v>
+        <v>-1.945557457336224</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="34">
       <c r="B21" s="39" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
-        <v>1.043437609697</v>
+        <v>1.046687654208</v>
       </c>
       <c r="D21" s="41" t="n">
-        <v>0.0005691090825197254</v>
+        <v>-0.000175054460501145</v>
       </c>
       <c r="E21" s="41" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>1.048735133696079</v>
+        <v>-0.322584489822125</v>
       </c>
     </row>
     <row r="22" ht="15.95" customHeight="1">
@@ -1537,18 +1537,18 @@
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="45">
       <c r="B24" s="43" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="43" t="inlineStr"/>
       <c r="D24" s="37" t="n">
-        <v>0.008768468951615427</v>
+        <v>-9.398179174890942e-06</v>
       </c>
       <c r="E24" s="37" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F24" s="38" t="n">
-        <v>0.8364172085267818</v>
+        <v>-0.002470067899634286</v>
       </c>
       <c r="G24" s="44" t="n"/>
     </row>
@@ -1561,13 +1561,13 @@
       </c>
       <c r="C25" s="52" t="inlineStr"/>
       <c r="D25" s="41" t="n">
-        <v>0.01094365095399463</v>
+        <v>0.006163387110292629</v>
       </c>
       <c r="E25" s="41" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F25" s="42" t="n">
-        <v>0.9435926638929504</v>
+        <v>0.5354614916050937</v>
       </c>
       <c r="G25" s="53" t="n"/>
     </row>
@@ -1580,13 +1580,13 @@
       </c>
       <c r="C26" s="52" t="inlineStr"/>
       <c r="D26" s="41" t="n">
-        <v>0.03875391642308346</v>
+        <v>0.03352321325201779</v>
       </c>
       <c r="E26" s="41" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F26" s="42" t="n">
-        <v>1.098213702357279</v>
+        <v>0.9524003787250493</v>
       </c>
       <c r="G26" s="53" t="n"/>
     </row>
@@ -1599,13 +1599,13 @@
       </c>
       <c r="C27" s="52" t="inlineStr"/>
       <c r="D27" s="41" t="n">
-        <v>0.03432778788653268</v>
+        <v>0.03624428033067595</v>
       </c>
       <c r="E27" s="41" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F27" s="42" t="n">
-        <v>1.05822502357559</v>
+        <v>0.9524087332901904</v>
       </c>
       <c r="G27" s="53" t="n"/>
     </row>
@@ -1637,13 +1637,13 @@
       </c>
       <c r="C29" s="52" t="inlineStr"/>
       <c r="D29" s="41" t="n">
-        <v>0.04536470086600008</v>
+        <v>0.04730164346199994</v>
       </c>
       <c r="E29" s="41" t="n">
-        <v>0.04043636873983614</v>
+        <v>0.0460962328228911</v>
       </c>
       <c r="F29" s="42" t="n">
-        <v>1.121878701766531</v>
+        <v>1.026149873108725</v>
       </c>
       <c r="G29" s="53" t="n"/>
     </row>
@@ -1671,7 +1671,7 @@
       <c r="C32" s="14" t="n"/>
       <c r="D32" s="14" t="n"/>
       <c r="E32" s="46" t="n">
-        <v>125653988.9099</v>
+        <v>125886811.5516</v>
       </c>
       <c r="F32" s="29" t="n"/>
       <c r="G32" s="4" t="n"/>
@@ -1686,7 +1686,7 @@
       <c r="C33" s="14" t="n"/>
       <c r="D33" s="14" t="n"/>
       <c r="E33" s="46" t="n">
-        <v>112333962.0829438</v>
+        <v>113958817.5569024</v>
       </c>
       <c r="F33" s="29" t="n"/>
       <c r="G33" s="4" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D35" s="20" t="n"/>
